--- a/task448/golden/rural_lender_recruitment_2027.xlsx
+++ b/task448/golden/rural_lender_recruitment_2027.xlsx
@@ -146,7 +146,7 @@
     <t>Lenders that do not report HMDA are counted from the Venridge purchase-money file, after removing quitclaim refinances into a family trust, re-recordings, second mortgages against the same deed, seller-carried notes and the second county's record of a farmstead mortgage, then divided by the share of the HMDA reporters' mortgages the file holds for the way the mortgage was recorded: 1,673 of the reporters' 1,731 mortgages recorded the same day as the deed (97 per cent), 236 of their 395 recorded after it (60 per cent).</t>
   </si>
   <si>
-    <t>County figures: each HMDA reporter's count is spread over the counties its recorded mortgages stand in (HMDA places some rural homes in the county of their postal city); the program year is counted from the recorder file for every lender, each mortgage over the capture of the way it was recorded.</t>
+    <t>County figures: a home counts in the county in which the property is recorded (program guidelines 2.2), so each HMDA reporter's count is spread over the counties its recorded mortgages stand in (HMDA places some rural homes in the county of their postal city); the program year is counted from the recorder file for every lender, each mortgage over the capture of the way it was recorded.</t>
   </si>
   <si>
     <t>Every count is estimated from unrounded figures and rounded to the nearest 10 once; the program year's total for all eight counties is rounded from the unrounded county figures, so it need not equal the sum of the rounded rows.</t>

--- a/task448/golden/rural_lender_recruitment_2027.xlsx
+++ b/task448/golden/rural_lender_recruitment_2027.xlsx
@@ -131,13 +131,13 @@
     <t>Rice, Ottawa, Ellsworth and Lincoln together</t>
   </si>
   <si>
-    <t>All eight counties, program year</t>
+    <t>All eight counties, program year (nearest 100)</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Counts are first-lien mortgages a bank, credit union or licensed mortgage company made to finance an arm's-length purchase of a home in Saline, McPherson, Dickinson, Marion, Rice, Ottawa, Ellsworth or Lincoln County, dated by closing (program guidelines 7.1 to 7.5).</t>
+    <t>Counts are first-lien mortgages a bank, credit union or licensed mortgage company made to finance an arm's-length purchase of a home in Saline, McPherson, Dickinson, Marion, Rice, Ottawa, Ellsworth or Lincoln County, dated by closing, every one a lender made whether or not a report or data file shows it (program guidelines 7.1 to 7.5).</t>
   </si>
   <si>
     <t>Lenders that report HMDA are counted from the 2024 and 2025 loan-level file: originations (action 1), home purchase (purpose 1), first lien, property in the eight counties.</t>
@@ -149,7 +149,7 @@
     <t>County figures: a home counts in the county in which the property is recorded (program guidelines 2.2), so each HMDA reporter's count is spread over the counties its recorded mortgages stand in (HMDA places some rural homes in the county of their postal city); the program year is counted from the recorder file for every lender, each mortgage over the capture of the way it was recorded.</t>
   </si>
   <si>
-    <t>Every count is estimated from unrounded figures and rounded to the nearest 10 once; the program year's total for all eight counties is rounded from the unrounded county figures, so it need not equal the sum of the rounded rows.</t>
+    <t>Every count is estimated from unrounded figures and rounded once: the program year's total for all eight counties to the nearest 100, every other count to the nearest 10.</t>
   </si>
   <si>
     <t>Prepared by the research desk, 9 October 2026, from the files pulled for the December board.</t>
@@ -875,7 +875,7 @@
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11">
-        <v>1610</v>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
